--- a/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-04T08:19:22+00:00</t>
+    <t>2023-07-04T09:29:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-04T09:29:05+00:00</t>
+    <t>2023-07-04T13:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
+++ b/ig/mc-changes-1.0.2/StructureDefinition-as-ext-practitioner-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-04T13:11:28+00:00</t>
+    <t>2023-07-10T13:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
